--- a/bases-box-tepic/entregables/Calendario-Bases-Box-Tepic-Ago-Sep-2026.xlsx
+++ b/bases-box-tepic/entregables/Calendario-Bases-Box-Tepic-Ago-Sep-2026.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Guía rápida" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Calendario" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Ideas de Stories" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guía rápida" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calendario" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ideas de Stories" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Calendario'!$A$1:$N$16</definedName>
@@ -1322,7 +1322,7 @@
       <c r="D42" s="27" t="n"/>
       <c r="E42" s="10" t="inlineStr">
         <is>
-          <t>Mínimo 4 días con stories por semana. La hoja «Ideas de Stories» trae 14 listas para usar.</t>
+          <t>Mínimo 4 días con stories por semana. Hay 14 ideas listas para usar.</t>
         </is>
       </c>
     </row>
@@ -2016,7 +2016,7 @@
         <is>
           <t>Diseño limpio, alto contraste:
 • Fondo papel #F4F2ED
-• Titular grafito #1A1A1A: «Cotización\nel mismo día»
+• Titular grafito #1A1A1A: «Cotización / el mismo día»
 • Ícono de WhatsApp en naranja #F2591F + el número 311 108 3374 EN GRANDE
 • Franja inferior grafito con dirección y horario
 El número va en la imagen, no solo en el copy.</t>
@@ -3062,7 +3062,7 @@
         <is>
           <t>Cierre de ciclo, alto contraste:
 • Fondo grafito #1A1A1A a página completa
-• Titular en papel #F4F2ED: «¿Este fin\ncambias tu base?»
+• Titular en papel #F4F2ED: «¿Este fin / cambias tu base?»
 • Los 5 puntos con palomitas naranja #F2591F
 • Barra inferior naranja con el WhatsApp 311 108 3374 en grafito
 Reutiliza la retícula del post #2 para cerrar consistente.</t>
